--- a/tasklist/venusfusion.xlsx
+++ b/tasklist/venusfusion.xlsx
@@ -4,26 +4,27 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="13" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="第１章LENR" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="第２章地球送電" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="第３章テザー空中駅" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="第4章都市間移動" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="運賃" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="都市間移動" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="第5章　金星テラフォーム" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="金星300年の大計" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="山頂" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="海" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="865炉拠点" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="都市" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="第6章水星・金星連成" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="エピローグ" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="第２章地球送電" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="第３章テザー空中駅" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="第4章都市間移動" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="運賃" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="都市間移動" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="第5章　金星テラフォーム" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="金星300年の大計" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="山頂" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="海" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="865炉拠点" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="都市" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="第6章水星・金星連成" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="エピローグ" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">第２章地球送電!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">第２章地球送電!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
   <si>
     <t>順序</t>
   </si>
@@ -103,6 +104,509 @@
   </si>
   <si>
     <t>やり残し</t>
+  </si>
+  <si>
+    <t>カテゴリ</t>
+  </si>
+  <si>
+    <t>計算テーマ</t>
+  </si>
+  <si>
+    <t>物理的意義</t>
+  </si>
+  <si>
+    <t>必要なパラメータ</t>
+  </si>
+  <si>
+    <t>優先度</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-001</t>
+  </si>
+  <si>
+    <t>環境条件</t>
+  </si>
+  <si>
+    <t>マクスウェル山頂の大気圧・温度プロファイル計算（修正版）</t>
+  </si>
+  <si>
+    <t>装置の熱管理と構造設計の基礎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">標高11km
+気温減率8.5-10℃/km
+大気組成CO2</t>
+  </si>
+  <si>
+    <t>緊急</t>
+  </si>
+  <si>
+    <t>山頂温度は350-370℃（従来の300℃から修正）</t>
+  </si>
+  <si>
+    <t>山頂25℃の前提崩れる</t>
+  </si>
+  <si>
+    <t>26.06.24</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-001b</t>
+  </si>
+  <si>
+    <t>高度55km浮遊プラットフォームの環境評価</t>
+  </si>
+  <si>
+    <t>25℃・1気圧環境の活用可能性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高度55km
+温度25℃
+気圧1気圧
+硫酸濃度</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>浮遊基地構想の基礎データ</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-002</t>
+  </si>
+  <si>
+    <t>日射量と太陽風の影響評価</t>
+  </si>
+  <si>
+    <t>エネルギー収支とプラズマ安定性の評価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">太陽定数2613W/m2
+アルベ0.77
+磁場強度</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>金星軌道は地球の約2倍の日射</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-003</t>
+  </si>
+  <si>
+    <t>地殻熱流量と地質安定性評価</t>
+  </si>
+  <si>
+    <t>装置の設置基盤の長期的安定性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">地殻厚
+熱流量
+地震活動度</t>
+  </si>
+  <si>
+    <t>マクスウェル山の火山活動履歴調査必要</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-004</t>
+  </si>
+  <si>
+    <t>核融合条件</t>
+  </si>
+  <si>
+    <t>常温核融合のQ値（エネルギー利得）計算</t>
+  </si>
+  <si>
+    <t>実用的なエネルギー生成の可否判断</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力エネルギー
+出力エネルギー
+Q値</t>
+  </si>
+  <si>
+    <t>触媒効率が鍵、高温環境が有利に働く可能性</t>
+  </si>
+  <si>
+    <t>26.06.26</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-005</t>
+  </si>
+  <si>
+    <t>パラジウム・ニッケル触媒の水素吸蔵特性計算（高温版）</t>
+  </si>
+  <si>
+    <t>350℃環境での触媒性能評価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温度350℃
+圧力50気圧
+水素濃度
+格子定数
+</t>
+  </si>
+  <si>
+    <t>超臨界CO2中での水素供給が課題</t>
+  </si>
+  <si>
+    <t>26.07.2</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-006</t>
+  </si>
+  <si>
+    <t>異常過剰熱の発生確率と再現性評価（高温環境版）</t>
+  </si>
+  <si>
+    <t>実用化に向けた信頼性評価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実験データ数
+成功確率
+統計的有意差</t>
+  </si>
+  <si>
+    <t>中部大学等のデータを350℃環境に外挿</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-007</t>
+  </si>
+  <si>
+    <t>エネルギー変換</t>
+  </si>
+  <si>
+    <t>熱電変換効率の最適化計算（高温差利用）</t>
+  </si>
+  <si>
+    <t>350℃と25℃（高度55km）の温度差利用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温度差325K
+ゼーベック係数
+熱伝導率</t>
+  </si>
+  <si>
+    <t>山頂-高度55km間の熱サイフォン構想</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-008</t>
+  </si>
+  <si>
+    <t>スターリングエンジン設計パラメータ計算（高温版）</t>
+  </si>
+  <si>
+    <t>機械的出力を取り出す代替手段</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温度差325K
+作動ガス(He)
+圧力比
+効率</t>
+  </si>
+  <si>
+    <t>超臨界CO2を作動流体とする方式も検討</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-009</t>
+  </si>
+  <si>
+    <t>蓄電システムの容量設計（金星日照サイクル対応）</t>
+  </si>
+  <si>
+    <t>夜間（金星の夜側）のエネルギー供給</t>
+  </si>
+  <si>
+    <t xml:space="preserve">発電量
+消費電力
+蓄電効率
+日照時間</t>
+  </si>
+  <si>
+    <t>金星の自転周期は約243地球日（昼126日・夜117日）</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-010</t>
+  </si>
+  <si>
+    <t>構造設計</t>
+  </si>
+  <si>
+    <t>装置の耐圧・耐食性評価（超臨界CO2環境）</t>
+  </si>
+  <si>
+    <t>50気圧・350℃CO2環境での長期運用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">圧力50気圧
+温度350℃
+材料腐食速度</t>
+  </si>
+  <si>
+    <t>超臨界CO2は溶媒としても活性</t>
+  </si>
+  <si>
+    <t>26.06.23</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-011</t>
+  </si>
+  <si>
+    <t>熱応力と熱膨張の解析（高温サイクル対応）</t>
+  </si>
+  <si>
+    <t>温度サイクルによる材料疲労評価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">熱膨張係数
+温度勾配
+ヤング率</t>
+  </si>
+  <si>
+    <t>昼夜の温度差は山頂でも100℃以上</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-012</t>
+  </si>
+  <si>
+    <t>軽量化と輸送コストのトレードオフ計算（高度55km基地案含む）</t>
+  </si>
+  <si>
+    <t>地球からの輸送効率</t>
+  </si>
+  <si>
+    <t>構造材密度</t>
+  </si>
+  <si>
+    <t>強度</t>
+  </si>
+  <si>
+    <t>打ち上げコスト</t>
+  </si>
+  <si>
+    <t>高度55km浮遊基地から山頂への資材輸送も検討</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-013</t>
+  </si>
+  <si>
+    <t>運用・制御</t>
+  </si>
+  <si>
+    <t>遠隔運用の通信遅延時間計算</t>
+  </si>
+  <si>
+    <t>地球からのリアルタイム制御の可否</t>
+  </si>
+  <si>
+    <t xml:space="preserve">地球-金星間距離
+光速
+通信プロトコル</t>
+  </si>
+  <si>
+    <t>往復で約5～28分の遅延（軌道位置依存）</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-014</t>
+  </si>
+  <si>
+    <t>自動運転AIの判断ロジック設計（高温対応版）</t>
+  </si>
+  <si>
+    <t>通信遅延を補う自律制御</t>
+  </si>
+  <si>
+    <t>センサー入力</t>
+  </si>
+  <si>
+    <t>異常検知アルゴリズム</t>
+  </si>
+  <si>
+    <t>フェイルセーフ</t>
+  </si>
+  <si>
+    <t>350℃で動作可能な電子機器の制約</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-015</t>
+  </si>
+  <si>
+    <t>装置寿命とメンテナンス間隔の最適化（無人運用）</t>
+  </si>
+  <si>
+    <t>無人運用の実現可能性</t>
+  </si>
+  <si>
+    <t>MTBF</t>
+  </si>
+  <si>
+    <t>MTTR</t>
+  </si>
+  <si>
+    <t>交換部品の寿命</t>
+  </si>
+  <si>
+    <t>金星での修理は不可能に近い</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-016</t>
+  </si>
+  <si>
+    <t>システム統合</t>
+  </si>
+  <si>
+    <t>総合エネルギー収支シミュレーション（山頂-55km連携案）</t>
+  </si>
+  <si>
+    <t>システム全体の正味エネルギー利得</t>
+  </si>
+  <si>
+    <t xml:space="preserve">発電量
+自己消費電力
+損失</t>
+  </si>
+  <si>
+    <t>Q値&gt;1の確認が必須</t>
+  </si>
+  <si>
+    <t>26.06.27</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-017</t>
+  </si>
+  <si>
+    <t>コスト対効果分析（C/P値）（山頂設置vs浮遊基地）</t>
+  </si>
+  <si>
+    <t>実用化の経済的妥当性</t>
+  </si>
+  <si>
+    <t>建設費</t>
+  </si>
+  <si>
+    <t>運用費</t>
+  </si>
+  <si>
+    <t>発電単価</t>
+  </si>
+  <si>
+    <t>両案の比較評価</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-018</t>
+  </si>
+  <si>
+    <t>リスクアセスメントと冗長性設計（高温・高圧・腐食環境）</t>
+  </si>
+  <si>
+    <t>装置故障時の安全確保</t>
+  </si>
+  <si>
+    <t xml:space="preserve">故障モード
+影響度
+対策コスト</t>
+  </si>
+  <si>
+    <t>放射能漏れのリスク評価も含む</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-019</t>
+  </si>
+  <si>
+    <t>文明評価</t>
+  </si>
+  <si>
+    <t>金星文明レベルとエネルギー消費量の相関</t>
+  </si>
+  <si>
+    <t>文明発展段階の客観的指標</t>
+  </si>
+  <si>
+    <t>エネルギー消費量</t>
+  </si>
+  <si>
+    <t>人口（想定）</t>
+  </si>
+  <si>
+    <t>技術レベル</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>カルダシェフスケールの応用</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-020</t>
+  </si>
+  <si>
+    <t>マクスウェル山頂設置の地政学的意義</t>
+  </si>
+  <si>
+    <t>国際協力と資源配分の最適化</t>
+  </si>
+  <si>
+    <t>設置国</t>
+  </si>
+  <si>
+    <t>運用権</t>
+  </si>
+  <si>
+    <t>利益配分</t>
+  </si>
+  <si>
+    <t>宇宙条約との整合性確認</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-021</t>
+  </si>
+  <si>
+    <t>新構想</t>
+  </si>
+  <si>
+    <t>山頂-高度55km間の熱サイフォン発電システム設計</t>
+  </si>
+  <si>
+    <t>350℃と25℃の温度差を利用した発電</t>
+  </si>
+  <si>
+    <t>温度差325K</t>
+  </si>
+  <si>
+    <t>作動流体(CO2)</t>
+  </si>
+  <si>
+    <t>パイプ長44km</t>
+  </si>
+  <si>
+    <t>効率</t>
+  </si>
+  <si>
+    <t>既存地熱発電の応用</t>
+  </si>
+  <si>
+    <t>LENR-VENUS-022</t>
+  </si>
+  <si>
+    <t>高度55km浮遊基地と山頂LENR装置の連携システム</t>
+  </si>
+  <si>
+    <t>有人運用拠点と無人発電所のハイブリッド</t>
+  </si>
+  <si>
+    <t>浮揚力</t>
+  </si>
+  <si>
+    <t>通信遅延</t>
+  </si>
+  <si>
+    <t>物資輸送</t>
+  </si>
+  <si>
+    <t>有人基地の居住性評価</t>
   </si>
   <si>
     <t>ステップ</t>
@@ -319,9 +823,6 @@
   </si>
   <si>
     <t>#302a</t>
-  </si>
-  <si>
-    <t>備考</t>
   </si>
   <si>
     <t>滑空軌道計算</t>
@@ -1993,10 +2494,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Noto Sans CJK JP"/>
     </font>
     <font>
@@ -2005,7 +2505,6 @@
     </font>
     <font>
       <sz val="10.500000"/>
-      <color indexed="64"/>
       <name val="IPAGothic"/>
     </font>
     <font>
@@ -2023,6 +2522,23 @@
       <sz val="10.500000"/>
       <color indexed="2"/>
       <name val="IPAGothic"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="5" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.000000"/>
@@ -2074,7 +2590,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -2097,18 +2613,27 @@
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="10" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="11" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -2116,7 +2641,7 @@
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -2745,94 +3270,106 @@
   </sheetPr>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="0" width="7.8799999999999999"/>
-    <col customWidth="1" min="2" max="2" style="0" width="5.75"/>
-    <col customWidth="1" min="3" max="3" style="0" width="9.3800000000000008"/>
+    <col customWidth="1" min="3" max="3" style="0" width="8.1300000000000008"/>
+    <col customWidth="1" min="4" max="4" style="0" width="16.890000000000001"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.149999999999999">
-      <c r="A1" s="7" t="s">
-        <v>225</v>
+    <row r="1" ht="32.799999999999997">
+      <c r="A1" s="10" t="s">
+        <v>359</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>226</v>
+      <c r="B1" s="10" t="s">
+        <v>360</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>227</v>
+      <c r="C1" s="10" t="s">
+        <v>361</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>228</v>
+      <c r="D1" s="10" t="s">
+        <v>362</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>229</v>
+    </row>
+    <row r="2" ht="64.150000000000006">
+      <c r="A2" s="12" t="s">
+        <v>363</v>
       </c>
-    </row>
-    <row r="2" ht="95.5">
-      <c r="A2" s="9" t="s">
-        <v>230</v>
+      <c r="B2" s="12" t="s">
+        <v>364</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>231</v>
+      <c r="C2" s="11">
+        <v>11</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>232</v>
+      <c r="D2" s="10" t="s">
+        <v>365</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>233</v>
+    </row>
+    <row r="3" ht="79.849999999999994">
+      <c r="A3" s="12" t="s">
+        <v>366</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>234</v>
+      <c r="B3" s="12" t="s">
+        <v>367</v>
       </c>
-    </row>
-    <row r="3" ht="95.5">
-      <c r="A3" s="9" t="s">
-        <v>235</v>
+      <c r="C3" s="11">
+        <v>5</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>236</v>
+      <c r="D3" s="10" t="s">
+        <v>368</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>237</v>
+    </row>
+    <row r="4" ht="64.150000000000006">
+      <c r="A4" s="12" t="s">
+        <v>369</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>238</v>
+      <c r="B4" s="12" t="s">
+        <v>370</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>239</v>
+      <c r="C4" s="11">
+        <v>8</v>
       </c>
-    </row>
-    <row r="4" ht="95.5">
-      <c r="A4" s="9" t="s">
-        <v>240</v>
+      <c r="D4" s="10" t="s">
+        <v>371</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>241</v>
+    </row>
+    <row r="5" ht="64.150000000000006">
+      <c r="A5" s="12" t="s">
+        <v>369</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>242</v>
+      <c r="B5" s="12" t="s">
+        <v>372</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>243</v>
+      <c r="C5" s="11">
+        <v>6</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>244</v>
+      <c r="D5" s="10" t="s">
+        <v>373</v>
       </c>
     </row>
-    <row r="5" ht="95.5">
-      <c r="A5" s="9" t="s">
-        <v>245</v>
+    <row r="6" ht="48.5">
+      <c r="A6" s="12" t="s">
+        <v>374</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>246</v>
+      <c r="B6" s="12" t="s">
+        <v>375</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>247</v>
+      <c r="C6" s="11">
+        <v>5.5</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>248</v>
+      <c r="D6" s="10" t="s">
+        <v>376</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>249</v>
+    </row>
+    <row r="7" ht="48.5">
+      <c r="A7" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C7" s="11">
+        <v>4</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -2851,65 +3388,94 @@
   </sheetPr>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="0" min="1" max="3" style="1" width="12.630000000000001"/>
-    <col customWidth="1" min="4" max="4" style="1" width="15.99"/>
-    <col customWidth="0" min="5" max="16384" style="1" width="12.630000000000001"/>
+    <col customWidth="1" min="1" max="1" style="0" width="7.8799999999999999"/>
+    <col customWidth="1" min="2" max="2" style="0" width="5.75"/>
+    <col customWidth="1" min="3" max="3" style="0" width="9.3800000000000008"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75">
-      <c r="A1" s="2" t="s">
-        <v>250</v>
+    <row r="1" ht="17.149999999999999">
+      <c r="A1" s="10" t="s">
+        <v>380</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>251</v>
+      <c r="B1" s="10" t="s">
+        <v>381</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>252</v>
+      <c r="C1" s="10" t="s">
+        <v>382</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>253</v>
+      <c r="D1" s="10" t="s">
+        <v>383</v>
       </c>
-    </row>
-    <row r="2" ht="43.25">
-      <c r="A2" s="3" t="s">
-        <v>254</v>
+      <c r="E1" s="10" t="s">
+        <v>384</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>255</v>
+    </row>
+    <row r="2" ht="95.5">
+      <c r="A2" s="12" t="s">
+        <v>385</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>256</v>
+      <c r="B2" s="14" t="s">
+        <v>386</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>257</v>
+      <c r="C2" s="12" t="s">
+        <v>387</v>
       </c>
-    </row>
-    <row r="3" ht="53.700000000000003">
-      <c r="A3" s="3" t="s">
-        <v>258</v>
+      <c r="D2" s="10" t="s">
+        <v>388</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>259</v>
+      <c r="E2" s="10" t="s">
+        <v>389</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>260</v>
+    </row>
+    <row r="3" ht="95.5">
+      <c r="A3" s="12" t="s">
+        <v>390</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>261</v>
+      <c r="B3" s="14" t="s">
+        <v>391</v>
       </c>
-    </row>
-    <row r="4" ht="53.700000000000003">
-      <c r="A4" s="3" t="s">
-        <v>262</v>
+      <c r="C3" s="12" t="s">
+        <v>392</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>263</v>
+      <c r="D3" s="10" t="s">
+        <v>393</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>264</v>
+      <c r="E3" s="10" t="s">
+        <v>394</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>265</v>
+    </row>
+    <row r="4" ht="95.5">
+      <c r="A4" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="5" ht="95.5">
+      <c r="A5" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -2928,92 +3494,65 @@
   </sheetPr>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="0" width="6.75"/>
-    <col customWidth="1" min="2" max="2" style="0" width="6"/>
+    <col customWidth="0" min="1" max="3" style="1" width="12.630000000000001"/>
+    <col customWidth="1" min="4" max="4" style="1" width="15.99"/>
+    <col customWidth="0" min="5" max="16384" style="1" width="12.630000000000001"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.799999999999997">
-      <c r="A1" s="7" t="s">
-        <v>226</v>
+    <row r="1" ht="15.75">
+      <c r="A1" s="2" t="s">
+        <v>405</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>251</v>
+      <c r="B1" s="2" t="s">
+        <v>406</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>266</v>
+      <c r="C1" s="2" t="s">
+        <v>407</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>267</v>
+      <c r="D1" s="2" t="s">
+        <v>408</v>
       </c>
     </row>
-    <row r="2" ht="64.150000000000006">
-      <c r="A2" s="8" t="s">
-        <v>268</v>
+    <row r="2" ht="43.25">
+      <c r="A2" s="3" t="s">
+        <v>409</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>269</v>
+      <c r="B2" s="2" t="s">
+        <v>410</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>270</v>
+      <c r="C2" s="3" t="s">
+        <v>411</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>271</v>
+      <c r="D2" s="2" t="s">
+        <v>412</v>
       </c>
     </row>
-    <row r="3" ht="79.849999999999994">
-      <c r="A3" s="8" t="s">
-        <v>272</v>
+    <row r="3" ht="53.700000000000003">
+      <c r="A3" s="3" t="s">
+        <v>413</v>
       </c>
-      <c r="B3" s="7">
-        <v>32</v>
+      <c r="B3" s="2" t="s">
+        <v>414</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>273</v>
+      <c r="C3" s="3" t="s">
+        <v>415</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>274</v>
+      <c r="D3" s="2" t="s">
+        <v>416</v>
       </c>
     </row>
-    <row r="4" ht="79.849999999999994">
-      <c r="A4" s="8" t="s">
-        <v>275</v>
+    <row r="4" ht="53.700000000000003">
+      <c r="A4" s="3" t="s">
+        <v>417</v>
       </c>
-      <c r="B4" s="7">
-        <v>128</v>
+      <c r="B4" s="2" t="s">
+        <v>418</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>276</v>
+      <c r="C4" s="3" t="s">
+        <v>419</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="5" ht="79.849999999999994">
-      <c r="A5" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="B5" s="7">
-        <v>512</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="6" ht="79.849999999999994">
-      <c r="A6" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="B6" s="8">
-        <v>865</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>283</v>
+      <c r="D4" s="2" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -3025,6 +3564,110 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" style="0" width="6.75"/>
+    <col customWidth="1" min="2" max="2" style="0" width="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32.799999999999997">
+      <c r="A1" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="2" ht="64.150000000000006">
+      <c r="A2" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="3" ht="79.849999999999994">
+      <c r="A3" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="B3" s="10">
+        <v>32</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4" ht="79.849999999999994">
+      <c r="A4" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="B4" s="10">
+        <v>128</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" ht="79.849999999999994">
+      <c r="A5" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="B5" s="10">
+        <v>512</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="6" ht="79.849999999999994">
+      <c r="A6" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="B6" s="11">
+        <v>865</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>438</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr filterMode="0">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -3043,111 +3686,111 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>148</v>
+        <v>303</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>284</v>
+        <v>439</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>285</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" ht="53.700000000000003">
       <c r="A2" s="3" t="s">
-        <v>286</v>
+        <v>441</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>287</v>
+        <v>442</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>288</v>
+        <v>443</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>289</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" ht="64.150000000000006">
       <c r="A3" s="3" t="s">
-        <v>290</v>
+        <v>445</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>291</v>
+        <v>446</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>292</v>
+        <v>447</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>293</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" ht="53.700000000000003">
       <c r="A4" s="3" t="s">
-        <v>294</v>
+        <v>449</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>295</v>
+        <v>450</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>296</v>
+        <v>451</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>297</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" ht="64.150000000000006">
       <c r="A5" s="3" t="s">
-        <v>298</v>
+        <v>453</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>299</v>
+        <v>454</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>300</v>
+        <v>455</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>301</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" ht="53.700000000000003">
       <c r="A6" s="3" t="s">
-        <v>302</v>
+        <v>457</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>303</v>
+        <v>458</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>459</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>305</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" ht="64.150000000000006">
       <c r="A7" s="3" t="s">
-        <v>306</v>
+        <v>461</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>307</v>
+        <v>462</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>308</v>
+        <v>463</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>309</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" ht="53.700000000000003">
       <c r="A8" s="3" t="s">
-        <v>310</v>
+        <v>465</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>311</v>
+        <v>466</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>312</v>
+        <v>467</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>313</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -3158,7 +3801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr filterMode="0">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -3178,13 +3821,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>314</v>
+        <v>469</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>315</v>
+        <v>470</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>316</v>
+        <v>471</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3211,10 +3854,10 @@
     </row>
     <row r="2" ht="63.75">
       <c r="A2" s="3" t="s">
-        <v>317</v>
+        <v>472</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>318</v>
+      <c r="B2" s="15" t="s">
+        <v>473</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="2"/>
@@ -31251,6 +31894,654 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="2" style="6" width="10.28125"/>
+    <col customWidth="1" min="3" max="3" style="6" width="15.7109375"/>
+    <col customWidth="1" min="4" max="4" style="6" width="16.28125"/>
+    <col customWidth="1" min="5" max="5" style="6" width="21.140625"/>
+    <col min="6" max="6" style="6" width="10.28125"/>
+    <col customWidth="1" min="7" max="7" style="6" width="13.7109375"/>
+    <col min="8" max="8" style="6" width="10.28125"/>
+    <col customWidth="1" min="9" max="9" style="6" width="17.8515625"/>
+    <col min="10" max="16384" style="6" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" ht="71.25">
+      <c r="A2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" ht="57">
+      <c r="A3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" ht="42.75">
+      <c r="A4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" ht="42.75">
+      <c r="A5" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" ht="57">
+      <c r="A6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" ht="71.25">
+      <c r="A7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" ht="57">
+      <c r="A8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" ht="57">
+      <c r="A9" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" ht="57">
+      <c r="A10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" ht="71.25">
+      <c r="A11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" ht="42.75">
+      <c r="A12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" ht="42.75">
+      <c r="A13" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" ht="71.25">
+      <c r="A14" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" ht="57">
+      <c r="A15" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" ht="42.75">
+      <c r="A16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" ht="57">
+      <c r="A17" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" ht="57">
+      <c r="A18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" ht="57">
+      <c r="A19" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" ht="57">
+      <c r="A20" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" ht="42.75">
+      <c r="A21" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" ht="42.75">
+      <c r="A22" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" ht="57">
+      <c r="A23" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" ht="57">
+      <c r="A24" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr filterMode="0">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
@@ -31266,7 +32557,7 @@
   <sheetData>
     <row r="1" ht="38.25">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -31275,13 +32566,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="G1" s="4"/>
     </row>
@@ -31293,16 +32584,16 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>183</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -31311,19 +32602,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>188</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>189</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>34</v>
+        <v>190</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -31332,22 +32623,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>191</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>39</v>
+        <v>195</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" ht="51">
@@ -31355,22 +32646,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>198</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" ht="63.75">
@@ -31378,22 +32669,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>201</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>202</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>203</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>48</v>
+        <v>204</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" ht="51">
@@ -31401,22 +32692,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>205</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>206</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>53</v>
+        <v>209</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" ht="51">
@@ -31424,19 +32715,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>54</v>
+        <v>210</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>57</v>
+        <v>213</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -31445,19 +32736,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>215</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -31466,19 +32757,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>218</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>64</v>
+        <v>220</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>65</v>
+        <v>221</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -34460,7 +35751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr filterMode="0">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -34479,7 +35770,7 @@
   <sheetData>
     <row r="1" ht="32.799999999999997">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -34491,10 +35782,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>66</v>
+        <v>222</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="G1" s="4"/>
     </row>
@@ -34503,22 +35794,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>224</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>70</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" ht="53.700000000000003">
@@ -34526,22 +35817,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>229</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>232</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" ht="53.700000000000003">
@@ -34549,22 +35840,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>236</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" ht="43.25">
@@ -34572,22 +35863,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>237</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>83</v>
+        <v>239</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" ht="43.25">
@@ -34595,22 +35886,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>241</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>244</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" ht="43.25">
@@ -34618,33 +35909,33 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>245</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>90</v>
+        <v>246</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>91</v>
+        <v>247</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>92</v>
+        <v>248</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" ht="15.75">
-      <c r="B8" s="6" t="s">
-        <v>93</v>
+      <c r="B8" s="9" t="s">
+        <v>249</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" ht="15.75">
-      <c r="B9" s="6" t="s">
-        <v>94</v>
+      <c r="B9" s="9" t="s">
+        <v>250</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -37620,146 +38911,6 @@
     </row>
     <row r="1000" ht="15.75">
       <c r="G1000" s="4"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" style="1" width="7.75"/>
-    <col customWidth="1" min="2" max="2" style="1" width="5.8799999999999999"/>
-    <col customWidth="0" min="3" max="16384" style="1" width="12.630000000000001"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22.350000000000001">
-      <c r="A1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" ht="43.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" ht="43.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" ht="43.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" ht="43.25">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" ht="43.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" ht="43.25">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>118</v>
-      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
@@ -37777,63 +38928,128 @@
   </sheetPr>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" style="0" width="8.6300000000000008"/>
-    <col customWidth="1" min="3" max="3" style="0" width="17.379999999999999"/>
+    <col customWidth="1" min="1" max="1" style="1" width="7.75"/>
+    <col customWidth="1" min="2" max="2" style="1" width="5.8799999999999999"/>
+    <col customWidth="0" min="3" max="16384" style="1" width="12.630000000000001"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.149999999999999">
-      <c r="A1" s="7" t="s">
-        <v>119</v>
+    <row r="1" ht="22.350000000000001">
+      <c r="A1" s="2" t="s">
+        <v>179</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>120</v>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>121</v>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="79.849999999999994">
-      <c r="A2" s="8" t="s">
-        <v>122</v>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>123</v>
+      <c r="E1" s="2" t="s">
+        <v>28</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>124</v>
+    </row>
+    <row r="2" ht="43.25">
+      <c r="A2" s="2">
+        <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="64.150000000000006">
-      <c r="A3" s="8" t="s">
-        <v>125</v>
+      <c r="B2" s="2" t="s">
+        <v>237</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>126</v>
+      <c r="C2" s="2" t="s">
+        <v>251</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>127</v>
+      <c r="D2" s="3" t="s">
+        <v>252</v>
       </c>
-    </row>
-    <row r="4" ht="64.150000000000006">
-      <c r="A4" s="8" t="s">
-        <v>128</v>
+      <c r="E2" s="2" t="s">
+        <v>253</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>126</v>
+    </row>
+    <row r="3" ht="43.25">
+      <c r="A3" s="2">
+        <v>2</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>129</v>
+      <c r="B3" s="2" t="s">
+        <v>254</v>
       </c>
-    </row>
-    <row r="5" ht="48.5">
-      <c r="A5" s="9" t="s">
-        <v>130</v>
+      <c r="C3" s="2" t="s">
+        <v>255</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>131</v>
+      <c r="D3" s="3" t="s">
+        <v>256</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>132</v>
+      <c r="E3" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" ht="43.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" ht="43.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" ht="43.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" ht="43.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -37851,49 +39067,64 @@
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" style="0" width="8.6300000000000008"/>
+    <col customWidth="1" min="3" max="3" style="0" width="17.379999999999999"/>
+  </cols>
   <sheetData>
     <row r="1" ht="17.149999999999999">
-      <c r="A1" s="7" t="s">
-        <v>133</v>
+      <c r="A1" s="10" t="s">
+        <v>274</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>134</v>
+      <c r="B1" s="10" t="s">
+        <v>275</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>135</v>
+      <c r="C1" s="10" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="2" ht="64.150000000000006">
-      <c r="A2" s="9" t="s">
-        <v>136</v>
+    <row r="2" ht="79.849999999999994">
+      <c r="A2" s="11" t="s">
+        <v>277</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>137</v>
+      <c r="B2" s="12" t="s">
+        <v>278</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>138</v>
+      <c r="C2" s="10" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="3" ht="64.150000000000006">
-      <c r="A3" s="9" t="s">
-        <v>139</v>
+      <c r="A3" s="11" t="s">
+        <v>280</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>140</v>
+      <c r="B3" s="12" t="s">
+        <v>281</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>141</v>
+      <c r="C3" s="10" t="s">
+        <v>282</v>
       </c>
     </row>
-    <row r="4" ht="79.849999999999994">
-      <c r="A4" s="9" t="s">
-        <v>142</v>
+    <row r="4" ht="64.150000000000006">
+      <c r="A4" s="11" t="s">
+        <v>283</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>143</v>
+      <c r="B4" s="12" t="s">
+        <v>281</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>144</v>
+      <c r="C4" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" ht="48.5">
+      <c r="A5" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -37905,6 +39136,66 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetData>
+    <row r="1" ht="17.149999999999999">
+      <c r="A1" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" ht="64.150000000000006">
+      <c r="A2" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="3" ht="64.150000000000006">
+      <c r="A3" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" ht="79.849999999999994">
+      <c r="A4" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr filterMode="0">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -37924,22 +39215,22 @@
   <sheetData>
     <row r="1" ht="22.350000000000001">
       <c r="A1" s="2" t="s">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>146</v>
+        <v>301</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>147</v>
+        <v>302</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>148</v>
+        <v>303</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>149</v>
+        <v>304</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>150</v>
+        <v>305</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -37964,25 +39255,25 @@
     </row>
     <row r="2" ht="74.599999999999994">
       <c r="A2" s="3" t="s">
-        <v>151</v>
+        <v>306</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>152</v>
+        <v>307</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>153</v>
+        <v>308</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>154</v>
+        <v>309</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -38008,13 +39299,13 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>156</v>
+        <v>311</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>157</v>
+        <v>312</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>158</v>
+        <v>313</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>11</v>
@@ -38044,13 +39335,13 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>160</v>
+        <v>315</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>161</v>
+        <v>316</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>11</v>
@@ -38078,19 +39369,19 @@
     </row>
     <row r="5" ht="74.599999999999994">
       <c r="A5" s="3" t="s">
-        <v>162</v>
+        <v>317</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>163</v>
+        <v>318</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>153</v>
+        <v>308</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>164</v>
+        <v>319</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>165</v>
+        <v>320</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
@@ -38120,13 +39411,13 @@
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
-        <v>156</v>
+        <v>311</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>167</v>
+        <v>322</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>15</v>
@@ -38154,19 +39445,19 @@
     </row>
     <row r="7" ht="74.599999999999994">
       <c r="A7" s="3" t="s">
-        <v>168</v>
+        <v>323</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>169</v>
+        <v>324</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>153</v>
+        <v>308</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>170</v>
+        <v>325</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>171</v>
+        <v>326</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>15</v>
@@ -38196,13 +39487,13 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="s">
-        <v>156</v>
+        <v>311</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>172</v>
+        <v>327</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>15</v>
@@ -38232,13 +39523,13 @@
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>174</v>
+        <v>329</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -66020,7 +67311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr filterMode="0">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -66039,22 +67330,22 @@
   <sheetData>
     <row r="1" ht="22.350000000000001">
       <c r="A1" s="2" t="s">
-        <v>176</v>
+        <v>331</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>177</v>
+        <v>332</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>178</v>
+        <v>333</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>179</v>
+        <v>334</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>180</v>
+        <v>335</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>181</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" ht="53.700000000000003">
@@ -66062,19 +67353,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>182</v>
+        <v>337</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>183</v>
+        <v>338</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>184</v>
+        <v>339</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>185</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" ht="43.25">
@@ -66082,19 +67373,19 @@
         <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="13">
         <v>0.98999999999999999</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>187</v>
+        <v>342</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>188</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" ht="43.25">
@@ -66102,19 +67393,19 @@
         <v>90</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>189</v>
+        <v>344</v>
       </c>
       <c r="C4" s="2">
         <v>8</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="13">
         <v>0.94999999999999996</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>187</v>
+        <v>342</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>190</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" ht="43.25">
@@ -66122,19 +67413,19 @@
         <v>150</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>191</v>
+        <v>346</v>
       </c>
       <c r="C5" s="2">
         <v>32</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="13">
         <v>0.80000000000000004</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>192</v>
+        <v>347</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" ht="32.799999999999997">
@@ -66142,19 +67433,19 @@
         <v>210</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>194</v>
+        <v>349</v>
       </c>
       <c r="C6" s="2">
         <v>128</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="13">
         <v>0.5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>195</v>
+        <v>350</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" ht="43.25">
@@ -66162,19 +67453,19 @@
         <v>270</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>197</v>
+        <v>352</v>
       </c>
       <c r="C7" s="2">
         <v>512</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="13">
         <v>0.10000000000000001</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>198</v>
+        <v>353</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>199</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" ht="53.700000000000003">
@@ -66182,137 +67473,19 @@
         <v>300</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="C8" s="3">
         <v>865</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>201</v>
+        <v>356</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>202</v>
+        <v>357</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col customWidth="1" min="3" max="3" style="0" width="8.1300000000000008"/>
-    <col customWidth="1" min="4" max="4" style="0" width="16.890000000000001"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32.799999999999997">
-      <c r="A1" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="2" ht="64.150000000000006">
-      <c r="A2" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C2" s="8">
-        <v>11</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="3" ht="79.849999999999994">
-      <c r="A3" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C3" s="8">
-        <v>5</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4" ht="64.150000000000006">
-      <c r="A4" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="8">
-        <v>8</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" ht="64.150000000000006">
-      <c r="A5" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C5" s="8">
-        <v>6</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" ht="48.5">
-      <c r="A6" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="8">
-        <v>5.5</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" ht="48.5">
-      <c r="A7" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C7" s="8">
-        <v>4</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>224</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/tasklist/venusfusion.xlsx
+++ b/tasklist/venusfusion.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="476">
   <si>
     <t>順序</t>
   </si>
@@ -253,7 +253,7 @@
     <t>超臨界CO2中での水素供給が課題</t>
   </si>
   <si>
-    <t>26.07.2</t>
+    <t>26.07.02</t>
   </si>
   <si>
     <t>LENR-VENUS-006</t>
@@ -293,6 +293,9 @@
     <t>山頂-高度55km間の熱サイフォン構想</t>
   </si>
   <si>
+    <t>26.07.04</t>
+  </si>
+  <si>
     <t>LENR-VENUS-008</t>
   </si>
   <si>
@@ -309,6 +312,9 @@
   </si>
   <si>
     <t>超臨界CO2を作動流体とする方式も検討</t>
+  </si>
+  <si>
+    <t>26.07.05</t>
   </si>
   <si>
     <t>LENR-VENUS-009</t>
@@ -2494,7 +2500,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10.000000"/>
       <name val="Noto Sans CJK JP"/>
@@ -2537,6 +2543,12 @@
     <font>
       <sz val="11.000000"/>
       <color theme="5" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11.000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -2590,7 +2602,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -2622,11 +2634,10 @@
     <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="10" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
@@ -2637,11 +2648,15 @@
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -3275,101 +3290,101 @@
   </cols>
   <sheetData>
     <row r="1" ht="32.799999999999997">
-      <c r="A1" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="2" ht="64.150000000000006">
-      <c r="A2" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="C2" s="11">
+    </row>
+    <row r="2" ht="64.150000000000006">
+      <c r="A2" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" s="12">
         <v>11</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="3" ht="79.849999999999994">
-      <c r="A3" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="C3" s="11">
+    </row>
+    <row r="3" ht="79.849999999999994">
+      <c r="A3" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="12">
         <v>5</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="4" ht="64.150000000000006">
-      <c r="A4" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="C4" s="11">
+    </row>
+    <row r="4" ht="64.150000000000006">
+      <c r="A4" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C4" s="12">
         <v>8</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="5" ht="64.150000000000006">
+      <c r="A5" s="13" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="5" ht="64.150000000000006">
-      <c r="A5" s="12" t="s">
-        <v>369</v>
+      <c r="B5" s="13" t="s">
+        <v>374</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="C5" s="11">
+      <c r="C5" s="12">
         <v>6</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="6" ht="48.5">
-      <c r="A6" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="C6" s="11">
+    </row>
+    <row r="6" ht="48.5">
+      <c r="A6" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" s="12">
         <v>5.5</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="7" ht="48.5">
-      <c r="A7" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="C7" s="11">
+    </row>
+    <row r="7" ht="48.5">
+      <c r="A7" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="C7" s="12">
         <v>4</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>379</v>
+      <c r="D7" s="11" t="s">
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -3394,88 +3409,88 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.149999999999999">
-      <c r="A1" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="2" ht="95.5">
-      <c r="A2" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="C2" s="12" t="s">
+    </row>
+    <row r="2" ht="95.5">
+      <c r="A2" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="C2" s="13" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="3" ht="95.5">
-      <c r="A3" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="C3" s="12" t="s">
+    </row>
+    <row r="3" ht="95.5">
+      <c r="A3" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="B3" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="C3" s="13" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="4" ht="95.5">
-      <c r="A4" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="E3" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="C4" s="12" t="s">
+    </row>
+    <row r="4" ht="95.5">
+      <c r="A4" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="C4" s="13" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="5" ht="95.5">
-      <c r="A5" s="12" t="s">
+      <c r="D4" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="C5" s="12" t="s">
+    </row>
+    <row r="5" ht="95.5">
+      <c r="A5" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="B5" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>404</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -3501,58 +3516,58 @@
   <sheetData>
     <row r="1" ht="15.75">
       <c r="A1" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" ht="43.25">
       <c r="A2" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" ht="53.700000000000003">
       <c r="A3" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" ht="53.700000000000003">
       <c r="A4" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -3576,87 +3591,87 @@
   </cols>
   <sheetData>
     <row r="1" ht="32.799999999999997">
-      <c r="A1" s="10" t="s">
-        <v>381</v>
+      <c r="A1" s="11" t="s">
+        <v>383</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>406</v>
+      <c r="B1" s="11" t="s">
+        <v>408</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="2" ht="64.150000000000006">
-      <c r="A2" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="C2" s="14" t="s">
+    </row>
+    <row r="2" ht="64.150000000000006">
+      <c r="A2" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="B2" s="15" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="3" ht="79.849999999999994">
-      <c r="A3" s="11" t="s">
+      <c r="C2" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="B3" s="10">
+      <c r="D2" s="13" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="3" ht="79.849999999999994">
+      <c r="A3" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="B3" s="11">
         <v>32</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="4" ht="79.849999999999994">
-      <c r="A4" s="11" t="s">
+      <c r="C3" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="B4" s="10">
+      <c r="D3" s="13" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" ht="79.849999999999994">
+      <c r="A4" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B4" s="11">
         <v>128</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="5" ht="79.849999999999994">
-      <c r="A5" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="B5" s="10">
+      <c r="D4" s="13" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="5" ht="79.849999999999994">
+      <c r="A5" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="B5" s="11">
         <v>512</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="6" ht="79.849999999999994">
-      <c r="A6" s="11" t="s">
+      <c r="C5" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="B6" s="11">
+      <c r="D5" s="13" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" ht="79.849999999999994">
+      <c r="A6" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="B6" s="12">
         <v>865</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>437</v>
+      <c r="C6" s="13" t="s">
+        <v>439</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>438</v>
+      <c r="D6" s="13" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -3686,111 +3701,111 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" ht="53.700000000000003">
       <c r="A2" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" ht="64.150000000000006">
       <c r="A3" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" ht="53.700000000000003">
       <c r="A4" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" ht="64.150000000000006">
       <c r="A5" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" ht="53.700000000000003">
       <c r="A6" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7" ht="64.150000000000006">
       <c r="A7" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" ht="53.700000000000003">
       <c r="A8" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -3821,13 +3836,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3854,10 +3869,10 @@
     </row>
     <row r="2" ht="63.75">
       <c r="A2" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>473</v>
+      <c r="B2" s="16" t="s">
+        <v>475</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="2"/>
@@ -32000,7 +32015,7 @@
       <c r="E4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>48</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -32023,7 +32038,7 @@
       <c r="E5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>48</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -32127,409 +32142,415 @@
       <c r="G9" s="6" t="s">
         <v>78</v>
       </c>
+      <c r="H9" s="6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="10" ht="57">
       <c r="A10" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
-      <c r="H10" s="6"/>
+      <c r="H10" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="11" ht="71.25">
       <c r="A11" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>48</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H11" s="6"/>
     </row>
     <row r="12" ht="42.75">
       <c r="A12" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="42.75">
       <c r="A13" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>48</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" ht="71.25">
       <c r="A14" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>42</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" ht="57">
-      <c r="A15" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="6" t="s">
+    </row>
+    <row r="15" s="9" customFormat="1" ht="57">
+      <c r="A15" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="B15" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="C15" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="D15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>113</v>
+      <c r="G15" s="9" t="s">
+        <v>115</v>
       </c>
+      <c r="I15" s="9"/>
     </row>
     <row r="16" ht="42.75">
       <c r="A16" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>42</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" ht="57">
       <c r="A17" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>42</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" ht="57">
       <c r="A18" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" ht="57">
       <c r="A19" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>42</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" ht="57">
       <c r="A20" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="6" t="s">
         <v>48</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" ht="42.75">
       <c r="A21" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" ht="42.75">
+      <c r="A22" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>151</v>
+      <c r="C22" s="6" t="s">
+        <v>159</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>152</v>
+      <c r="D22" s="6" t="s">
+        <v>160</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>153</v>
+      <c r="E22" s="6" t="s">
+        <v>161</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>154</v>
+      <c r="F22" s="6" t="s">
+        <v>162</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>155</v>
+      <c r="G22" s="6" t="s">
+        <v>163</v>
       </c>
-    </row>
-    <row r="22" ht="42.75">
-      <c r="A22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="I22" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" ht="57">
       <c r="A23" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" ht="57">
       <c r="A24" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>42</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -32557,7 +32578,7 @@
   <sheetData>
     <row r="1" ht="38.25">
       <c r="A1" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -32566,13 +32587,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G1" s="4"/>
     </row>
@@ -32584,16 +32605,16 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -32602,19 +32623,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -32623,22 +32644,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" ht="51">
@@ -32646,22 +32667,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" ht="63.75">
@@ -32669,22 +32690,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" ht="51">
@@ -32692,22 +32713,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" ht="51">
@@ -32715,19 +32736,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -32736,19 +32757,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -32757,19 +32778,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -35770,7 +35791,7 @@
   <sheetData>
     <row r="1" ht="32.799999999999997">
       <c r="A1" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -35782,10 +35803,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G1" s="4"/>
     </row>
@@ -35794,22 +35815,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" ht="53.700000000000003">
@@ -35817,22 +35838,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" ht="53.700000000000003">
@@ -35840,22 +35861,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" ht="43.25">
@@ -35863,22 +35884,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" ht="43.25">
@@ -35886,22 +35907,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" ht="43.25">
@@ -35909,33 +35930,33 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" ht="15.75">
-      <c r="B8" s="9" t="s">
-        <v>249</v>
+      <c r="B8" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" ht="15.75">
-      <c r="B9" s="9" t="s">
-        <v>250</v>
+      <c r="B9" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -38935,7 +38956,7 @@
   <sheetData>
     <row r="1" ht="22.350000000000001">
       <c r="A1" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -38955,16 +38976,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" ht="43.25">
@@ -38972,16 +38993,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" ht="43.25">
@@ -38989,16 +39010,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" ht="43.25">
@@ -39006,16 +39027,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" ht="43.25">
@@ -39023,16 +39044,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" ht="43.25">
@@ -39040,16 +39061,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -39073,58 +39094,58 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.149999999999999">
-      <c r="A1" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="2" ht="79.849999999999994">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="C2" s="10" t="s">
+    </row>
+    <row r="2" ht="79.849999999999994">
+      <c r="A2" s="12" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="3" ht="64.150000000000006">
-      <c r="A3" s="11" t="s">
+      <c r="B2" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="C3" s="10" t="s">
+    </row>
+    <row r="3" ht="64.150000000000006">
+      <c r="A3" s="12" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="4" ht="64.150000000000006">
-      <c r="A4" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="5" ht="48.5">
-      <c r="A5" s="12" t="s">
+    <row r="4" ht="64.150000000000006">
+      <c r="A4" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B4" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="C5" s="12" t="s">
+    </row>
+    <row r="5" ht="48.5">
+      <c r="A5" s="13" t="s">
         <v>287</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -39144,47 +39165,47 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" ht="17.149999999999999">
-      <c r="A1" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="2" ht="64.150000000000006">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C2" s="10" t="s">
+    </row>
+    <row r="2" ht="64.150000000000006">
+      <c r="A2" s="13" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="3" ht="64.150000000000006">
-      <c r="A3" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="C3" s="10" t="s">
+    </row>
+    <row r="3" ht="64.150000000000006">
+      <c r="A3" s="13" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="4" ht="79.849999999999994">
-      <c r="A4" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="C4" s="10" t="s">
+    </row>
+    <row r="4" ht="79.849999999999994">
+      <c r="A4" s="13" t="s">
         <v>299</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -39215,22 +39236,22 @@
   <sheetData>
     <row r="1" ht="22.350000000000001">
       <c r="A1" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -39255,25 +39276,25 @@
     </row>
     <row r="2" ht="74.599999999999994">
       <c r="A2" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -39299,13 +39320,13 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>11</v>
@@ -39335,13 +39356,13 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>11</v>
@@ -39369,19 +39390,19 @@
     </row>
     <row r="5" ht="74.599999999999994">
       <c r="A5" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
@@ -39411,13 +39432,13 @@
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>15</v>
@@ -39445,19 +39466,19 @@
     </row>
     <row r="7" ht="74.599999999999994">
       <c r="A7" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>15</v>
@@ -39487,13 +39508,13 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>15</v>
@@ -39523,13 +39544,13 @@
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -67330,22 +67351,22 @@
   <sheetData>
     <row r="1" ht="22.350000000000001">
       <c r="A1" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" ht="53.700000000000003">
@@ -67353,19 +67374,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" ht="43.25">
@@ -67373,19 +67394,19 @@
         <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="14">
         <v>0.98999999999999999</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" ht="43.25">
@@ -67393,19 +67414,19 @@
         <v>90</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C4" s="2">
         <v>8</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="14">
         <v>0.94999999999999996</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" ht="43.25">
@@ -67413,19 +67434,19 @@
         <v>150</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C5" s="2">
         <v>32</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="14">
         <v>0.80000000000000004</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" ht="32.799999999999997">
@@ -67433,19 +67454,19 @@
         <v>210</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C6" s="2">
         <v>128</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="14">
         <v>0.5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" ht="43.25">
@@ -67453,19 +67474,19 @@
         <v>270</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C7" s="2">
         <v>512</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="14">
         <v>0.10000000000000001</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" ht="53.700000000000003">
@@ -67473,19 +67494,19 @@
         <v>300</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C8" s="3">
         <v>865</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
